--- a/src/test/resources/data/logInData/logInData.xlsx
+++ b/src/test/resources/data/logInData/logInData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\Documents\Automation\ParaBank\src\test\resources\data\logInData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA5F214-7309-4D24-BBA6-29B291BF8C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED73B69-9F7F-44E4-8649-27879CA0BC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="5325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
